--- a/public/templates/forms/A-091-ThreatIntelligenceRoutingDistributionMatrix-FORM.xlsx
+++ b/public/templates/forms/A-091-ThreatIntelligenceRoutingDistributionMatrix-FORM.xlsx
@@ -1,59 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Matrix" sheetId="1" r:id="rId1"/>
-    <sheet name="Column Instructions" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="11">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF1B3A5C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,18 +122,140 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -360,381 +543,506 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="26"/>
-    <col min="2" max="2" customWidth="1" width="16"/>
-    <col min="3" max="3" customWidth="1" width="22"/>
-    <col min="4" max="4" customWidth="1" width="22"/>
-    <col min="5" max="5" customWidth="1" width="16"/>
-    <col min="6" max="6" customWidth="1" width="28"/>
-    <col min="7" max="7" customWidth="1" width="24"/>
-    <col min="8" max="8" customWidth="1" width="26"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" t="str">
-        <v>Threat Intelligence Routing &amp; Distribution Matrix</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Threat Intelligence Routing &amp; Distribution Matrix</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1"/>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="str">
-        <v>Authority</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3" t="str">
-        <v>Adopted by {agencyName} under the authority of {signingOfficialTitle}.</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Adopted by [Agency Name] under the authority of [signing official / title].</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4" t="str">
-        <v>[Role title]   « use a role, not a person’s name »</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>[Role title]   « use a role, not a person’s name »</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="str">
-        <v>Version / Dates</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5" t="str">
-        <v>Version {version}      Effective Date {effectiveDate}      Next Review {effectiveDate}</v>
-      </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Version / Dates</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Version [#]      Effective Date [Date]      Next Review [Date]</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" t="str">
-        <v>Classification</v>
-      </c>
-      <c r="B6"/>
-      <c r="C6" t="str">
-        <v>Restricted   « Minimum for this matrix as published with role-based recipients. Raise to Confidential if the PSAP identifies recipients by name rather than role, or if the matrix carries other PII. An agency may raise this floor but not lower it. »</v>
-      </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Restricted   « Minimum for this matrix as published with role-based recipients. Raise to Confidential if the PSAP identifies recipients by name rather than role, or if the matrix carries other PII. An agency may raise this floor but not lower it. »</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1"/>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="str">
-        <v>Purpose and Scope</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Purpose and Scope</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="str">
-        <v>Maps each threat-intelligence source the Agency relies on to the people who receive it, how often they receive it, and how an alert escalates into action. It answers two questions for leadership: how the Agency stays aware of threats that could disrupt 9-1-1 operations, and who acts when a threat is credible. Scope covers external feeds, partnerships, and vendor advisories that bear on the availability or security of call-handling, dispatch, and network systems.</v>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Maps each threat-intelligence source the Agency relies on to the people who receive it, how often they receive it, and how an alert escalates into action. It answers two questions for leadership: how the Agency stays aware of threats that could disrupt 9-1-1 operations, and who acts when a threat is credible. Scope covers external feeds, partnerships, and vendor advisories that bear on the availability or security of call-handling, dispatch, and network systems.</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1"/>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="str">
-        <v>How to Read This Matrix</v>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>How to Read This Matrix</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" t="str">
-        <v>Two tables. The first lists the intelligence sources the Agency subscribes to. The second routes each source to recipients, sets the cadence, states the action on receipt, and names the escalation path. Read a routing row as: this source goes to these roles, on this cadence, and escalates this way when the trigger is met.</v>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Two tables. The first lists the intelligence sources the Agency subscribes to. The second routes each source to recipients, sets the cadence, states the action on receipt, and names the escalation path. Read a routing row as: this source goes to these roles, on this cadence, and escalates this way when the trigger is met.</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1"/>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="str">
-        <v>Threat Intelligence Sources &amp; Subscriptions</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Threat Intelligence Sources &amp; Subscriptions</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1">
-      <c r="A15" t="str">
-        <v>« List each feed, partnership, or advisory service the Agency subscribes to. One row per source (e.g., MS-ISAC, EI-ISAC, CISA, Indiana IOT / IN-ISAC, CAD/ESInet vendor advisories). »</v>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>« List each feed, partnership, or advisory service the Agency subscribes to. One row per source (e.g., MS-ISAC, EI-ISAC, CISA, Indiana IOT / IN-ISAC, CAD/ESInet vendor advisories). »</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" t="str">
-        <v>Source / Feed</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Source Type</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Subscription / Access Status</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Access Method / Point of Contact (Role)</v>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Source / Feed</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Subscription / Access Status</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Access Method / Point of Contact (Role)</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" t="str">
-        <v>[Source name]</v>
-      </c>
-      <c r="B17" t="str">
-        <v>[ISAC / government / vendor / peer]</v>
-      </c>
-      <c r="C17" t="str">
-        <v>[Active / Pending / None]</v>
-      </c>
-      <c r="D17" t="str">
-        <v>[Portal login / email list / Owner role]</v>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>[Source name]</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>[ISAC / government / vendor / peer]</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>[Active / Pending / None]</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>[Portal login / email list / Owner role]</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="str">
-        <v>Routing &amp; Distribution Matrix</v>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Routing &amp; Distribution Matrix</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" t="str">
-        <v>« One row per source above. State who receives it, how often, what to do on receipt, and the escalation path. Escalation routes into the Incident Notification &amp; Escalation Contact List. »</v>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>« One row per source above. State who receives it, how often, what to do on receipt, and the escalation path. Escalation routes into the Incident Notification &amp; Escalation Contact List. »</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" t="str">
-        <v>Source / Feed</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Source Type</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Primary Recipient (Role)</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Secondary Recipient(s)</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Distribution Cadence</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Action on Receipt</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Escalation Trigger</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Escalation Route</v>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Source / Feed</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Primary Recipient (Role)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Secondary Recipient(s)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Distribution Cadence</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Action on Receipt</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Escalation Trigger</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Escalation Route</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" t="str">
-        <v>[Source name]</v>
-      </c>
-      <c r="B27" t="str">
-        <v>[ISAC / gov / vendor]</v>
-      </c>
-      <c r="C27" t="str">
-        <v>{reviewerRole}</v>
-      </c>
-      <c r="D27" t="str">
-        <v>[Role(s)]</v>
-      </c>
-      <c r="E27" t="str">
-        <v>[Real-time / daily / weekly]</v>
-      </c>
-      <c r="F27" t="str">
-        <v>[Review / log / brief leadership]</v>
-      </c>
-      <c r="G27" t="str">
-        <v>[Credible threat to 9-1-1 ops]</v>
-      </c>
-      <c r="H27" t="str">
-        <v>[→ Incident Notification &amp; Escalation Contact List]</v>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>[Source name]</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>[ISAC / gov / vendor]</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>[Role]</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>[Role(s)]</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>[Real-time / daily / weekly]</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>[Review / log / brief leadership]</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>[Credible threat to 9-1-1 ops]</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>[→ Incident Notification &amp; Escalation Contact List]</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1"/>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="str">
-        <v>Notes and Exceptions</v>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Notes and Exceptions</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="27.75" customHeight="1">
-      <c r="A36" t="str">
-        <v>« Anything the grid cannot capture: handling caveats, restricted-source restrictions, effective dates, and the cross-reference to the Incident Response Plan. »</v>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>« Anything the grid cannot capture: handling caveats, restricted-source restrictions, effective dates, and the cross-reference to the Incident Response Plan. »</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="str">
-        <v>[Notes and exceptions.]</v>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>[Notes and exceptions.]</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1"/>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="str">
-        <v>Review Schedule and Ownership</v>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Review Schedule and Ownership</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="str">
-        <v>Reviewed at least [annually] by the {ownerRole}, and whenever a source is added or dropped.</v>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Reviewed at least [annually] by the [Owner role], and whenever a source is added or dropped.</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1"/>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="str">
-        <v>Source Authority</v>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Source Authority</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" t="str">
-        <v>« List only the authorities that map to this artifact. Group by authority; order numerically. No padding. »</v>
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>« List only the authorities that map to this artifact. Group by authority; order numerically. No padding. »</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="str">
-        <v>NENA-STA-040.2-2024: §4.1.1, §4.3.2, §5.6</v>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>NENA-STA-040.2-2024: §4.1.1, §4.3.2, §5.6</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="str">
-        <v>NIST SP 800-53 Rev. 5: PM-15, PM-16, SI-5, IR-6</v>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>NIST SP 800-53 Rev. 5: PM-15, PM-16, SI-5, IR-6</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1"/>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="str">
-        <v>Revision History</v>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Revision History</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
-      <c r="A48" t="str">
-        <v>Version</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Author</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Summary of Change</v>
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Summary of Change</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" t="str">
-        <v>{version}</v>
-      </c>
-      <c r="B49" t="str">
-        <v>{effectiveDate}</v>
-      </c>
-      <c r="C49" t="str">
-        <v>{reviewerRole}</v>
-      </c>
-      <c r="D49" t="str">
-        <v>{revisionNote}</v>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>[#]</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>[Date]</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>[Role]</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>[Initial issue]</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1"/>
     <row r="51" ht="44" customHeight="1">
-      <c r="A51" t="str">
-        <v>Drafter’s note (internal, delete before publishing): Ships at Restricted on the basis of role-based recipients; raise to Confidential if the PSAP names individuals. Confirm the Agency’s actual subscriptions before publishing. The escalation path routes into the Incident Notification &amp; Escalation Contact List; keep the two documents aligned.</v>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Drafter’s note (internal, delete before publishing): Ships at Restricted on the basis of role-based recipients; raise to Confidential if the PSAP names individuals. Confirm the Agency’s actual subscriptions before publishing. The escalation path routes into the Incident Notification &amp; Escalation Contact List; keep the two documents aligned.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -769,179 +1077,326 @@
     <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H51"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="24"/>
-    <col min="2" max="2" customWidth="1" width="50"/>
-    <col min="3" max="3" customWidth="1" width="14"/>
-    <col min="4" max="4" customWidth="1" width="34"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" t="str">
-        <v>Column Instructions &amp; How to Use</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Column Instructions &amp; How to Use</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" t="str">
-        <v>How to use this form: this is the Threat Intelligence Routing &amp; Distribution Matrix. Fill the header block on the Matrix tab, list the Agency’s sources in the first table, then route each source in the second table. Replace every [BRACKETED] field and delete every « guidance » note before publishing.</v>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>How to use this form: this is the Threat Intelligence Routing &amp; Distribution Matrix. Fill the header block on the Matrix tab, list the Agency’s sources in the first table, then route each source in the second table. Replace every [BRACKETED] field and delete every « guidance » note before publishing.</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" t="str">
-        <v>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule, source authority and revision history live on the Matrix tab.</v>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule, source authority and revision history live on the Matrix tab.</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="str">
-        <v>The routing matrix columns</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>The routing matrix columns</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="str">
-        <v>Column</v>
-      </c>
-      <c r="B6" t="str">
-        <v>What it holds</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Required?</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Example value</v>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>What it holds</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Required?</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Example value</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" t="str">
-        <v>Source / Feed</v>
-      </c>
-      <c r="B7" t="str">
-        <v>The intelligence source the row routes. Matches a row in the Sources table.</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D7" t="str">
-        <v>MS-ISAC advisory</v>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Source / Feed</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>The intelligence source the row routes. Matches a row in the Sources table.</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>MS-ISAC advisory</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" t="str">
-        <v>Source Type</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Category of the source.</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D8" t="str">
-        <v>ISAC / government / vendor / peer</v>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Category of the source.</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>ISAC / government / vendor / peer</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" t="str">
-        <v>Primary Recipient (Role)</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Role that receives the source first. A role, not a person’s name in the form.</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Security Coordinator</v>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Primary Recipient (Role)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Role that receives the source first. A role, not a person’s name in the form.</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Security Coordinator</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" t="str">
-        <v>Secondary Recipient(s)</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Other roles copied or briefed.</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Director, IT Support Lead</v>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Secondary Recipient(s)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Other roles copied or briefed.</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Director, IT Support Lead</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" t="str">
-        <v>Distribution Cadence</v>
-      </c>
-      <c r="B11" t="str">
-        <v>How often the source is distributed.</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Real-time / daily / weekly</v>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Distribution Cadence</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>How often the source is distributed.</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Real-time / daily / weekly</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" t="str">
-        <v>Action on Receipt</v>
-      </c>
-      <c r="B12" t="str">
-        <v>What the recipient does with it.</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Review, log, brief leadership</v>
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Action on Receipt</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>What the recipient does with it.</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Review, log, brief leadership</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" t="str">
-        <v>Escalation Trigger</v>
-      </c>
-      <c r="B13" t="str">
-        <v>The condition that escalates the item.</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Credible threat to 9-1-1 operations</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Escalation Trigger</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>The condition that escalates the item.</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Credible threat to 9-1-1 operations</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" t="str">
-        <v>Escalation Route</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Where a triggered item goes.</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Incident Notification &amp; Escalation Contact List</v>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Escalation Route</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Where a triggered item goes.</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Incident Notification &amp; Escalation Contact List</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profile Scaling Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSAP Profile</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum-viable implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small (1–5, no in-house IT)</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintain this by hand. One person, usually the director, keeps it current on the review cycle in the header block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium (6–25, shared county IT)</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A named coordinator owns it, updates it on a set cadence, and reconciles it at each periodic review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large (25+, dedicated IT/security)</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where a system of record exists (asset, identity, badge, or finance system), populate it from there on a schedule and treat this sheet as the reviewed record.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/forms/A-091-ThreatIntelligenceRoutingDistributionMatrix-FORM.xlsx
+++ b/public/templates/forms/A-091-ThreatIntelligenceRoutingDistributionMatrix-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -302,7 +302,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -336,7 +336,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-091-ThreatIntelligenceRoutingDistributionMatrix-FORM.xlsx
+++ b/public/templates/forms/A-091-ThreatIntelligenceRoutingDistributionMatrix-FORM.xlsx
@@ -4,12 +4,15 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Matrix!$26:$26</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,7 +549,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -708,7 +711,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="50.5" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>[Source name]</t>
@@ -817,7 +820,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>[Source name]</t>
@@ -1076,7 +1079,8 @@
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1084,7 +1088,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1102,14 +1106,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
           <t>How to use this form: this is the Threat Intelligence Routing &amp; Distribution Matrix. Fill the header block on the Matrix tab, list the Agency’s sources in the first table, then route each source in the second table. Replace every [BRACKETED] field and delete every « guidance » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule, source authority and revision history live on the Matrix tab.</t>
@@ -1146,7 +1150,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Source / Feed</t>
@@ -1190,7 +1194,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Primary Recipient (Role)</t>
@@ -1300,7 +1304,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Escalation Route</t>
@@ -1397,6 +1401,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>